--- a/tests/fixtures/agenda-valida.xlsx
+++ b/tests/fixtures/agenda-valida.xlsx
@@ -41,13 +41,13 @@
     <t>06/01/2025 09:00</t>
   </si>
   <si>
-    <t>DEMO-CL-001</t>
-  </si>
-  <si>
-    <t>DEMO-DR-001</t>
-  </si>
-  <si>
-    <t>PAC-A1</t>
+    <t>CLINIC-001</t>
+  </si>
+  <si>
+    <t>DOCTOR-001</t>
+  </si>
+  <si>
+    <t>PATIENT-001</t>
   </si>
   <si>
     <t>Realizada</t>
@@ -59,7 +59,7 @@
     <t>06/01/2025 09:30</t>
   </si>
   <si>
-    <t>PAC-B2</t>
+    <t>PATIENT-002</t>
   </si>
   <si>
     <t>Faltou</t>
@@ -71,10 +71,10 @@
     <t>07/01/2025 14:15</t>
   </si>
   <si>
-    <t>DEMO-DR-002</t>
-  </si>
-  <si>
-    <t>PAC-C3</t>
+    <t>DOCTOR-002</t>
+  </si>
+  <si>
+    <t>PATIENT-003</t>
   </si>
   <si>
     <t>Agendada</t>
@@ -86,10 +86,10 @@
     <t>07/01/2025 15:00</t>
   </si>
   <si>
-    <t>DEMO-CL-002</t>
-  </si>
-  <si>
-    <t>PAC-D4</t>
+    <t>CLINIC-002</t>
+  </si>
+  <si>
+    <t>PATIENT-004</t>
   </si>
   <si>
     <t>Cancelada</t>
@@ -101,7 +101,7 @@
     <t>08/01/2025 10:00</t>
   </si>
   <si>
-    <t>PAC-E5</t>
+    <t>PATIENT-005</t>
   </si>
   <si>
     <t>SYN-0006</t>
@@ -110,7 +110,7 @@
     <t>30/03/2025 10:30</t>
   </si>
   <si>
-    <t>PAC-F6</t>
+    <t>PATIENT-006</t>
   </si>
   <si>
     <t>observacao</t>
